--- a/employment_forms/028_pharmaceutical_lab_technician_employment_form--employment_forms.xlsx
+++ b/employment_forms/028_pharmaceutical_lab_technician_employment_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"bachelor's_degree_or_higher",_'value':_'bachelors_or_higher'}</t>
+          <t>bachelor's_degree_or_higher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "Bachelor's degree or higher", 'value': 'bachelors_or_higher'}</t>
+          <t>Bachelor's degree or higher</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"associate's_degree_or_higher",_'value':_'associates_or_higher'}</t>
+          <t>associate's_degree_or_higher</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Associate's degree or higher", 'value': 'associates_or_higher'}</t>
+          <t>Associate's degree or higher</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'some_college',_'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Some college', 'value': 'some_college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'osha_certification',_'value':_'osha'}</t>
+          <t>osha_certification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'OSHA certification', 'value': 'osha'}</t>
+          <t>OSHA certification</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday_to_friday',_'value':_'mon_to_fri'}</t>
+          <t>monday_to_friday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday to Friday', 'value': 'mon_to_fri'}</t>
+          <t>Monday to Friday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'every_day',_'value':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Every day', 'value': 'every_day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rotating_shifts',_'value':_'rotating_shifts'}</t>
+          <t>rotating_shifts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rotating shifts', 'value': 'rotating_shifts'}</t>
+          <t>Rotating shifts</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'8-12_hours',_'value':_'8-12'}</t>
+          <t>8-12_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '8-12 hours', 'value': '8-12'}</t>
+          <t>8-12 hours</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'13-16_hours',_'value':_'13-16'}</t>
+          <t>13-16_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '13-16 hours', 'value': '13-16'}</t>
+          <t>13-16 hours</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'17-20_hours',_'value':_'17-20'}</t>
+          <t>17-20_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '17-20 hours', 'value': '17-20'}</t>
+          <t>17-20 hours</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full_time',_'value':_'full_time'}</t>
+          <t>full_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full time', 'value': 'full_time'}</t>
+          <t>Full time</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part_time',_'value':_'part_time'}</t>
+          <t>part_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part time', 'value': 'part_time'}</t>
+          <t>Part time</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clinical',_'value':_'clinical'}</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clinical', 'value': 'clinical'}</t>
+          <t>Clinical</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lab',_'value':_'lab'}</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lab', 'value': 'lab'}</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'certification_1',_'value':_'certification_1'}</t>
+          <t>certification_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Certification 1', 'value': 'certification_1'}</t>
+          <t>Certification 1</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'certification_2',_'value':_'certification_2'}</t>
+          <t>certification_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Certification 2', 'value': 'certification_2'}</t>
+          <t>Certification 2</t>
         </is>
       </c>
     </row>
